--- a/server/data/trip_planner_50_countries_with_image_links.xlsx
+++ b/server/data/trip_planner_50_countries_with_image_links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alame\Documents\ExploreX\server\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B127D7-8930-430E-947F-C9DE9AFD54D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD533DE-9EF9-4B70-AE5C-BE94940DED12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Countries" sheetId="1" r:id="rId1"/>
@@ -73,9 +73,6 @@
     <t>Big Ben</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/fc/Big_Ben_2022.jpg</t>
-  </si>
-  <si>
     <t>Japan</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
     <t>Great Wall</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/10/Great_Wall_of_China_Mutianyu.jpg</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
@@ -115,18 +109,12 @@
     <t>Niagara Falls</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/2/2c/Niagara_Falls_from_USA.jpg</t>
-  </si>
-  <si>
     <t>Germany</t>
   </si>
   <si>
     <t>Neuschwanstein Castle</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Schloss_Neuschwanstein_2013.jpg</t>
-  </si>
-  <si>
     <t>Spain</t>
   </si>
   <si>
@@ -142,9 +130,6 @@
     <t>Matterhorn</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Matterhorn_from_Domhütte_-_2.jpg</t>
-  </si>
-  <si>
     <t>Thailand</t>
   </si>
   <si>
@@ -461,6 +446,21 @@
   </si>
   <si>
     <t>https://www.lot.com/content/dam/lot/lot-com/destination-photos/japonia/Tokyo-5%20.coreimg.jpg/1723628368208/Tokyo-5%20.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.britannica.com/31/91731-050-503D355A/Big-Ben-Houses-of-Parliament-London-England.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.britannica.com/89/179589-138-3EE27C94/Overview-Great-Wall-of-China.jpg?w=800&amp;h=450&amp;c=crop</t>
+  </si>
+  <si>
+    <t>https://globalgirltravels.com/wp-content/uploads/2016/10/Niagara-Falls-mist-aerial-bldgs-H_02a801c50_22359.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.britannica.com/27/101827-004-3236235E/Neuschwanstein-Castle-Bavarian-Alps-Germany.jpg</t>
+  </si>
+  <si>
+    <t>https://cdn.britannica.com/32/75732-050-8B294308/Matterhorn-Alpine-valley.jpg</t>
   </si>
 </sst>
 </file>
@@ -837,7 +837,7 @@
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -848,7 +848,7 @@
       <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
     </row>
@@ -859,7 +859,7 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
     </row>
@@ -870,7 +870,7 @@
       <c r="B5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -881,486 +881,499 @@
       <c r="B6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" t="s">
-        <v>17</v>
+      <c r="C6" s="1" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
-        <v>19</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
+      <c r="C8" s="1" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B9" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>37</v>
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
-        <v>40</v>
+        <v>35</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" t="s">
-        <v>43</v>
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B28" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C29" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C30" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C33" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C35" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C41" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C42" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B44" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C44" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C45" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B46" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C46" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C47" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C48" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="B49" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C7" r:id="rId1" xr:uid="{22474648-8872-49FD-BF8F-A8562D7EA2EE}"/>
+    <hyperlink ref="C2" r:id="rId2" xr:uid="{73957E57-99D0-40BF-A2E2-B31057F0B145}"/>
+    <hyperlink ref="C3" r:id="rId3" xr:uid="{4C010332-52C2-45E6-81FA-98F89B009D62}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{AA11EC35-4721-4FFA-917A-CD3A2CAEEF8C}"/>
+    <hyperlink ref="C5" r:id="rId5" xr:uid="{5B32D110-056D-4C72-B32D-F45D516C3ABF}"/>
+    <hyperlink ref="C6" r:id="rId6" xr:uid="{60337F24-0E68-4140-8EF0-32404E5A4329}"/>
+    <hyperlink ref="C8" r:id="rId7" xr:uid="{3A896CAB-227B-44A1-9D2A-A2AE8CFF4D29}"/>
+    <hyperlink ref="C9" r:id="rId8" xr:uid="{F2FA9576-F088-41FD-AE65-A7A0BC0FB38A}"/>
+    <hyperlink ref="C10" r:id="rId9" xr:uid="{EDB31B00-B25F-4B82-9411-25516721A37E}"/>
+    <hyperlink ref="C11" r:id="rId10" xr:uid="{5107CE6D-EBD2-4E8C-BA9B-3E7D20542E55}"/>
+    <hyperlink ref="C12" r:id="rId11" xr:uid="{E444CAFE-81D9-49D7-9098-2B94A7BEBB91}"/>
+    <hyperlink ref="C13" r:id="rId12" xr:uid="{CB8175F6-C109-497E-B723-C33A2ACE9373}"/>
+    <hyperlink ref="C14" r:id="rId13" xr:uid="{44925261-C0E6-412A-B53F-0F46E9BD7D26}"/>
+    <hyperlink ref="C15" r:id="rId14" xr:uid="{740612D5-DB8B-41EE-BEFD-1B0FC5476DC2}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
